--- a/results/metrics_modelling4_6-neural_networks.xlsx
+++ b/results/metrics_modelling4_6-neural_networks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH3"/>
+  <dimension ref="A1:DH5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1024,7 +1024,7 @@
         <v>0.8775510204081632</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9035493827160493</v>
+        <v>0.9097222222222222</v>
       </c>
       <c r="J2" t="n">
         <v>0.8233908948194661</v>
@@ -1042,342 +1042,342 @@
         <v>0.7692307692307692</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9225589225589226</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9424083769633508</v>
+        <v>0.9473684210526315</v>
       </c>
       <c r="Q2" t="n">
         <v>0.9375</v>
       </c>
       <c r="R2" t="n">
-        <v>0.9399477806788512</v>
+        <v>0.9424083769633508</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9759672619047619</v>
+        <v>0.9768105158730159</v>
       </c>
       <c r="T2" t="n">
-        <v>0.9154715206711792</v>
+        <v>0.9193173960288452</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9163690476190476</v>
+        <v>0.9211309523809523</v>
       </c>
       <c r="V2" t="n">
-        <v>0.8867924528301887</v>
+        <v>0.8878504672897196</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8952380952380953</v>
+        <v>0.9047619047619048</v>
       </c>
       <c r="X2" t="n">
-        <v>0.8909952606635072</v>
+        <v>0.8962264150943396</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>18.679642915725708, 22.204664945602417, 12.127790212631226, 7.912220001220703, 21.158206939697266, 6.587566137313843, 9.543040037155151</t>
+          <t>8.546937704086304, 16.00730609893799, 21.973552942276, 8.87303614616394, 23.701798915863037, 7.494261980056763, 12.607545852661133</t>
         </is>
       </c>
       <c r="Z2" t="n">
-        <v>14.03044731276376</v>
+        <v>14.17206280572074</v>
       </c>
       <c r="AA2" t="n">
-        <v>12.12779021263123</v>
+        <v>12.60754585266113</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.045351516288036</v>
+        <v>6.115667113901556</v>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0216829776763916, 0.021537065505981445, 0.016887664794921875, 0.11007905006408691, 0.02432703971862793, 0.017799854278564453, 0.01901388168334961</t>
+          <t>0.016965150833129883, 0.028533935546875, 0.020534038543701172, 0.015566825866699219, 0.02306079864501953, 0.015857934951782227, 0.038900136947631836</t>
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>0.0330467905317034</v>
+        <v>0.02277411733354841</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.02153706550598145</v>
+        <v>0.02053403854370117</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.03153710290190068</v>
+        <v>0.007854451644335177</v>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.9444444444444444, 0.7735849056603774, 0.8867924528301887, 0.8490566037735849, 0.9056603773584906, 0.7924528301886793, 0.8301886792452831</t>
+          <t>0.9629629629629629, 0.7735849056603774, 0.9056603773584906, 0.8490566037735849, 0.9433962264150944, 0.8301886792452831, 0.8301886792452831</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.9330827067669173, 0.7746031746031746, 0.8885448916408669, 0.8591331269349844, 0.903250773993808, 0.8150154798761611, 0.8095975232198143</t>
+          <t>0.9593984962406015, 0.7746031746031746, 0.914860681114551, 0.8591331269349844, 0.9326625386996904, 0.8560371517027863, 0.8095975232198143</t>
         </is>
       </c>
       <c r="AI2" t="n">
-        <v>0.8547468110051037</v>
+        <v>0.872327527502229</v>
       </c>
       <c r="AJ2" t="n">
         <v>0.8591331269349844</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.0530373673245501</v>
+        <v>0.0620544777551749</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.854597184785864</v>
+        <v>0.8707197763801536</v>
       </c>
       <c r="AM2" t="n">
         <v>0.8490566037735849</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.05703119240054517</v>
+        <v>0.06347275375466438</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.9577464788732395, 0.8181818181818182, 0.9090909090909091, 0.8749999999999999, 0.9253731343283583, 0.819672131147541, 0.8695652173913043</t>
+          <t>0.9714285714285714, 0.8181818181818182, 0.923076923076923, 0.8749999999999999, 0.9565217391304348, 0.8524590163934426, 0.8695652173913043</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.918918918918919, 0.7000000000000001, 0.8500000000000001, 0.8095238095238095, 0.8717948717948718, 0.7555555555555555, 0.7567567567567567</t>
+          <t>0.9473684210526315, 0.7000000000000001, 0.8780487804878049, 0.8095238095238095, 0.918918918918919, 0.7999999999999999, 0.7567567567567567</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.8089357017928448</v>
+        <v>0.8300880981057032</v>
       </c>
       <c r="AR2" t="n">
         <v>0.8095238095238095</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.07088549640409765</v>
+        <v>0.08243993348990079</v>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.9383326988960792, 0.7590909090909091, 0.8795454545454546, 0.8422619047619047, 0.898584003061615, 0.7876138433515483, 0.8131609870740305</t>
+          <t>0.9593984962406015, 0.7590909090909091, 0.900562851782364, 0.8422619047619047, 0.937720329024677, 0.8262295081967213, 0.8131609870740305</t>
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>0.8455128286830773</v>
+        <v>0.8626321408816012</v>
       </c>
       <c r="AV2" t="n">
         <v>0.8422619047619047</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.0591228120460382</v>
+        <v>0.06692104333067238</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.8820899555733102</v>
+        <v>0.8951761836574993</v>
       </c>
       <c r="AY2" t="n">
         <v>0.8749999999999999</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.04857066419041878</v>
+        <v>0.05233415130726372</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.9444444444444444, 0.8709677419354839, 0.9375, 0.9333333333333333, 0.9393939393939394, 0.9259259259259259, 0.8571428571428571</t>
+          <t>0.9714285714285714, 0.8709677419354839, 0.967741935483871, 0.9333333333333333, 0.9428571428571428, 0.9629629629629629, 0.8571428571428571</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.9444444444444444, 0.6363636363636364, 0.8095238095238095, 0.7391304347826086, 0.85, 0.6538461538461539, 0.7777777777777778</t>
+          <t>0.9473684210526315, 0.6363636363636364, 0.8181818181818182, 0.7391304347826086, 0.9444444444444444, 0.6923076923076923, 0.7777777777777778</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.7730123223912043</v>
+        <v>0.7936534607015157</v>
       </c>
       <c r="BD2" t="n">
         <v>0.7777777777777778</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.1004939903388957</v>
+        <v>0.1103265940028003</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.9155297488822833</v>
+        <v>0.9294906493063175</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9428571428571428</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.03318368973058714</v>
+        <v>0.04341643710481806</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.9714285714285714, 0.7714285714285715, 0.8823529411764706, 0.8235294117647058, 0.9117647058823529, 0.7352941176470589, 0.8823529411764706</t>
+          <t>0.9714285714285714, 0.7714285714285715, 0.8823529411764706, 0.8235294117647058, 0.9705882352941176, 0.7647058823529411, 0.8823529411764706</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.8947368421052632, 0.7777777777777778, 0.8947368421052632, 0.8947368421052632, 0.8947368421052632, 0.8947368421052632, 0.7368421052631579</t>
+          <t>0.9473684210526315, 0.7777777777777778, 0.9473684210526315, 0.8947368421052632, 0.8947368421052632, 0.9473684210526315, 0.7368421052631579</t>
         </is>
       </c>
       <c r="BK2" t="n">
-        <v>0.8554720133667502</v>
+        <v>0.8780284043441938</v>
       </c>
       <c r="BL2" t="n">
         <v>0.8947368421052632</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.06303976434390471</v>
+        <v>0.08014827037735309</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.8540216086434574</v>
+        <v>0.8666266506602641</v>
       </c>
       <c r="BO2" t="n">
         <v>0.8823529411764706</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.07613108055052155</v>
+        <v>0.07891584614121566</v>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.9864661654135338, 0.8603174603174604, 0.978328173374613, 0.9349845201238391, 0.9535603715170279, 0.9179566563467492, 0.8947368421052632</t>
+          <t>0.9894736842105263, 0.865079365079365, 0.978328173374613, 0.9411764705882353, 0.9504643962848297, 0.9179566563467492, 0.9024767801857585</t>
         </is>
       </c>
       <c r="BR2" t="n">
-        <v>0.9323357413140695</v>
+        <v>0.9349936465814396</v>
       </c>
       <c r="BS2" t="n">
-        <v>0.9349845201238391</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="BT2" t="n">
-        <v>0.04193528292906471</v>
+        <v>0.04028317535352828</v>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.8710691823899371, 0.9184952978056427, 0.890282131661442, 0.8934169278996865, 0.8714733542319749, 0.890282131661442, 0.9059561128526645</t>
+          <t>0.8710691823899371, 0.9216300940438872, 0.8871473354231975, 0.8996865203761756, 0.9090909090909091, 0.8871473354231975, 0.9122257053291536</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.8801424562918195, 0.9190629011553273, 0.8910774121488101, 0.8974997852049145, 0.878511899647736, 0.8950726007388952, 0.9072085230689921</t>
+          <t>0.8801424562918195, 0.9215019255455712, 0.8886502276827906, 0.9023541541369533, 0.9056405189449266, 0.8906478219778331, 0.912062892001031</t>
         </is>
       </c>
       <c r="BW2" t="n">
-        <v>0.8955107968937849</v>
+        <v>0.9001428566544177</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.8950726007388952</v>
+        <v>0.9023541541369533</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.01331213090125685</v>
+        <v>0.01339330009813834</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0.8915678769289699</v>
+        <v>0.8982852974394939</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.890282131661442</v>
+        <v>0.8996865203761756</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.01586919261411978</v>
+        <v>0.01624308417078171</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.8946015424164525, 0.9353233830845771, 0.912718204488778, 0.9145728643216081, 0.8956743002544529, 0.91183879093199, 0.9253731343283583</t>
+          <t>0.8946015424164525, 0.9379652605459058, 0.9099999999999999, 0.92, 0.9287469287469288, 0.9095477386934674, 0.9306930693069307</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.8340080971659919, 0.8898305084745763, 0.8523206751054851, 0.8583333333333333, 0.8326530612244899, 0.8547717842323652, 0.8728813559322035</t>
+          <t>0.8340080971659919, 0.8936170212765957, 0.8487394957983193, 0.8655462184873949, 0.8744588744588744, 0.85, 0.8803418803418804</t>
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>0.8563998307812064</v>
+        <v>0.8638159410755796</v>
       </c>
       <c r="CF2" t="n">
-        <v>0.8547717842323652</v>
+        <v>0.8655462184873949</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.01881328618566639</v>
+        <v>0.01921370020600778</v>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.8643048197912222, 0.9125769457795767, 0.8825194397971317, 0.8864530988274707, 0.8641636807394715, 0.8833052875821776, 0.899127245130281</t>
+          <t>0.8643048197912222, 0.9157911409112507, 0.8793697478991596, 0.8927731092436975, 0.9016029016029016, 0.8797738693467336, 0.9055174748244056</t>
         </is>
       </c>
       <c r="CI2" t="n">
-        <v>0.8846357882353332</v>
+        <v>0.8913047233741958</v>
       </c>
       <c r="CJ2" t="n">
-        <v>0.8833052875821776</v>
+        <v>0.8927731092436975</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.01618075511012185</v>
+        <v>0.01653651633359422</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.9128717456894595</v>
+        <v>0.918793505672812</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.9127182044887781</v>
+        <v>0.92</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01359567983789379</v>
+        <v>0.01392707073242354</v>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>0.9456521739130435, 0.9543147208121827, 0.9384615384615385, 0.9479166666666666, 0.9411764705882353, 0.9476439790575916, 0.9489795918367347</t>
+          <t>0.9456521739130435, 0.9545454545454546, 0.9381443298969072, 0.9484536082474226, 0.9402985074626866, 0.9427083333333334, 0.9494949494949495</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>0.7686567164179104, 0.860655737704918, 0.8145161290322581, 0.8110236220472441, 0.7727272727272727, 0.8046875, 0.8373983739837398</t>
+          <t>0.7686567164179104, 0.8677685950413223, 0.808, 0.824, 0.8559322033898306, 0.8031496062992126, 0.8512396694214877</t>
         </is>
       </c>
       <c r="CQ2" t="n">
-        <v>0.8099521931304776</v>
+        <v>0.8255352557956804</v>
       </c>
       <c r="CR2" t="n">
-        <v>0.8110236220472441</v>
+        <v>0.824</v>
       </c>
       <c r="CS2" t="n">
-        <v>0.03038996036377498</v>
+        <v>0.03254551537688833</v>
       </c>
       <c r="CT2" t="n">
-        <v>0.9463064487622848</v>
+        <v>0.9456139081276854</v>
       </c>
       <c r="CU2" t="n">
-        <v>0.9476439790575916</v>
+        <v>0.9456521739130435</v>
       </c>
       <c r="CV2" t="n">
-        <v>0.004839528805036431</v>
+        <v>0.005283272965667944</v>
       </c>
       <c r="CW2" t="inlineStr">
         <is>
-          <t>0.848780487804878, 0.9170731707317074, 0.8883495145631068, 0.883495145631068, 0.8543689320388349, 0.8786407766990292, 0.9029126213592233</t>
+          <t>0.848780487804878, 0.9219512195121952, 0.883495145631068, 0.8932038834951457, 0.9174757281553398, 0.8786407766990292, 0.912621359223301</t>
         </is>
       </c>
       <c r="CX2" t="inlineStr">
         <is>
-          <t>0.911504424778761, 0.9210526315789473, 0.8938053097345132, 0.911504424778761, 0.9026548672566371, 0.911504424778761, 0.911504424778761</t>
+          <t>0.911504424778761, 0.9210526315789473, 0.8938053097345132, 0.911504424778761, 0.8938053097345132, 0.9026548672566371, 0.911504424778761</t>
         </is>
       </c>
       <c r="CY2" t="n">
-        <v>0.9090757868121632</v>
+        <v>0.9065473418058421</v>
       </c>
       <c r="CZ2" t="n">
         <v>0.911504424778761</v>
       </c>
       <c r="DA2" t="n">
-        <v>0.007941335063868736</v>
+        <v>0.009441485710361448</v>
       </c>
       <c r="DB2" t="n">
-        <v>0.8819458069754068</v>
+        <v>0.8937383715029937</v>
       </c>
       <c r="DC2" t="n">
-        <v>0.883495145631068</v>
+        <v>0.8932038834951457</v>
       </c>
       <c r="DD2" t="n">
-        <v>0.02264096339157259</v>
+        <v>0.02411387314996457</v>
       </c>
       <c r="DE2" t="inlineStr">
         <is>
-          <t>0.9622490826678178, 0.9731279418057339, 0.9646232494200533, 0.9698642495059713, 0.9657831428816909, 0.9659334994415328, 0.9753200446773778</t>
+          <t>0.9629829484135548, 0.9747111681643132, 0.9650957986081279, 0.9702079216427528, 0.9699501675401667, 0.965632786321849, 0.9754918807457685</t>
         </is>
       </c>
       <c r="DF2" t="n">
-        <v>0.9681287443428825</v>
+        <v>0.9691532387766475</v>
       </c>
       <c r="DG2" t="n">
-        <v>0.9659334994415328</v>
+        <v>0.9699501675401667</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.004422323506991887</v>
+        <v>0.004468066086377373</v>
       </c>
     </row>
     <row r="3">
@@ -1414,7 +1414,7 @@
         <v>0.7906976744186046</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9690909090909091</v>
+        <v>0.9700000000000001</v>
       </c>
       <c r="J3" t="n">
         <v>0.8532927624429472</v>
@@ -1432,62 +1432,62 @@
         <v>0.9158878504672897</v>
       </c>
       <c r="O3" t="n">
-        <v>0.9225589225589226</v>
+        <v>0.9259259259259259</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8043478260869565</v>
+        <v>0.8064516129032258</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.9367088607594937</v>
+        <v>0.9493670886075949</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8654970760233918</v>
+        <v>0.8720930232558139</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9731738474044827</v>
+        <v>0.9729415863430496</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9055617767823815</v>
+        <v>0.9099801609170066</v>
       </c>
       <c r="U3" t="n">
-        <v>0.927070026710022</v>
+        <v>0.9333991406340727</v>
       </c>
       <c r="V3" t="n">
-        <v>0.975609756097561</v>
+        <v>0.9803921568627451</v>
       </c>
       <c r="W3" t="n">
         <v>0.9174311926605505</v>
       </c>
       <c r="X3" t="n">
-        <v>0.9456264775413712</v>
+        <v>0.9478672985781992</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>7.006517171859741, 4.8198418617248535, 7.344151973724365, 20.58397889137268, 7.975060939788818, 6.960787057876587, 8.22217869758606</t>
+          <t>4.664698839187622, 5.488649845123291, 6.283062934875488, 21.015094995498657, 9.712095022201538, 7.686125755310059, 17.938038110733032</t>
         </is>
       </c>
       <c r="Z3" t="n">
-        <v>8.987502370561872</v>
+        <v>10.39825221470424</v>
       </c>
       <c r="AA3" t="n">
-        <v>7.344151973724365</v>
+        <v>7.686125755310059</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.843123219469243</v>
+        <v>5.991717809499814</v>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.017177104949951172, 0.017117023468017578, 0.016655921936035156, 0.021413087844848633, 0.0159454345703125, 0.016022920608520508, 0.11894726753234863</t>
+          <t>0.01603984832763672, 0.015447139739990234, 0.19947290420532227, 0.020657062530517578, 0.015071868896484375, 0.015560150146484375, 0.03685569763183594</t>
         </is>
       </c>
       <c r="AD3" t="n">
-        <v>0.0318969658442906</v>
+        <v>0.04558638163975307</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.01711702346801758</v>
+        <v>0.01603984832763672</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.03557991770011582</v>
+        <v>0.06323746541017609</v>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
@@ -1617,157 +1617,937 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.9641025641025641, 0.8974358974358975, 0.9780219780219781, 0.9578754578754579, 0.9835164835164835, 0.9395604395604397, 0.9981684981684982</t>
+          <t>0.9658119658119658, 0.8974358974358975, 0.978021978021978, 0.9578754578754579, 0.9835164835164835, 0.9358974358974359, 1.0</t>
         </is>
       </c>
       <c r="BR3" t="n">
-        <v>0.9598116169544741</v>
+        <v>0.9597941740798884</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.9641025641025641</v>
+        <v>0.9658119658119658</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.03090952187112305</v>
+        <v>0.0316476433120521</v>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.9213836477987422, 0.9059561128526645, 0.890282131661442, 0.9278996865203761, 0.9090909090909091, 0.9216300940438872, 0.9090909090909091</t>
+          <t>0.9025157232704403, 0.9059561128526645, 0.890282131661442, 0.9278996865203761, 0.9090909090909091, 0.9216300940438872, 0.8934169278996865</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.9275030525030525, 0.9096782302664655, 0.9064856711915535, 0.9321266968325792, 0.9155605832076421, 0.9315987933634993, 0.9155605832076421</t>
+          <t>0.9184981684981685, 0.9096782302664655, 0.9102312719959779, 0.9321266968325792, 0.9155605832076421, 0.9315987933634993, 0.9086224233283057</t>
         </is>
       </c>
       <c r="BW3" t="n">
-        <v>0.919787658653205</v>
+        <v>0.9180451667846627</v>
       </c>
       <c r="BX3" t="n">
         <v>0.9155605832076421</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.00975530489365032</v>
+        <v>0.009321398735820226</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.9121904987227042</v>
+        <v>0.9072559407627721</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.9059561128526645</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0117013891560123</v>
+        <v>0.01276118734468142</v>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.8633879781420766, 0.8387096774193548, 0.8205128205128205, 0.8743169398907105, 0.8449197860962567, 0.8663101604278074, 0.8449197860962567</t>
+          <t>0.837696335078534, 0.8387096774193548, 0.8223350253807107, 0.8743169398907105, 0.8449197860962567, 0.8663101604278074, 0.8247422680412371</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.944812362030905, 0.9336283185840708, 0.9209932279909707, 0.9494505494505495, 0.9356984478935698, 0.9445676274944568, 0.9356984478935698</t>
+          <t>0.9303370786516854, 0.9336283185840708, 0.9206349206349208, 0.9494505494505495, 0.9356984478935698, 0.9445676274944568, 0.9234234234234234</t>
         </is>
       </c>
       <c r="CE3" t="n">
-        <v>0.9378355687625846</v>
+        <v>0.9339629094475252</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.9356984478935698</v>
+        <v>0.9336283185840708</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.008778252375773276</v>
+        <v>0.009690302832235405</v>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.9041001700864908, 0.8861689980017128, 0.8707530242518956, 0.91188374467063, 0.8903091169949133, 0.9054388939611321, 0.8903091169949133</t>
+          <t>0.8840167068651097, 0.8861689980017128, 0.8714849730078158, 0.91188374467063, 0.8903091169949133, 0.9054388939611321, 0.8740828457323302</t>
         </is>
       </c>
       <c r="CI3" t="n">
-        <v>0.8941375807088126</v>
+        <v>0.8890550398905205</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.8903091169949133</v>
+        <v>0.8861689980017128</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.01299202647538043</v>
+        <v>0.01392706015106879</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.8504395926550404</v>
+        <v>0.8441471703335158</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.8449197860962567</v>
+        <v>0.8387096774193548</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.01725358120318853</v>
+        <v>0.01822678392313382</v>
       </c>
       <c r="CO3" t="inlineStr">
         <is>
-          <t>0.797979797979798, 0.7722772277227723, 0.7272727272727273, 0.8163265306122449, 0.7745098039215687, 0.7941176470588235, 0.7745098039215687</t>
+          <t>0.7476635514018691, 0.7722772277227723, 0.7232142857142857, 0.8163265306122449, 0.7745098039215687, 0.7941176470588235, 0.7339449541284404</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
         <is>
-          <t>0.9771689497716894, 0.9678899082568807, 0.9760765550239234, 0.9773755656108597, 0.9723502304147466, 0.9815668202764977, 0.9723502304147466</t>
+          <t>0.981042654028436, 0.9678899082568807, 0.9806763285024155, 0.9773755656108597, 0.9723502304147466, 0.9815668202764977, 0.9761904761904762</t>
         </is>
       </c>
       <c r="CQ3" t="n">
-        <v>0.974968322824192</v>
+        <v>0.9767274261829018</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.9760765550239234</v>
+        <v>0.9773755656108597</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.004126892510423689</v>
+        <v>0.004714790132869196</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.7795705054985005</v>
+        <v>0.7660077143657149</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.7745098039215687</v>
+        <v>0.7722772277227723</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0260247071298681</v>
+        <v>0.030774642515355</v>
       </c>
       <c r="CW3" t="inlineStr">
         <is>
-          <t>0.9404761904761905, 0.9176470588235294, 0.9411764705882353, 0.9411764705882353, 0.9294117647058824, 0.9529411764705882, 0.9294117647058824</t>
+          <t>0.9523809523809523, 0.9176470588235294, 0.9529411764705882, 0.9411764705882353, 0.9294117647058824, 0.9529411764705882, 0.9411764705882353</t>
         </is>
       </c>
       <c r="CX3" t="inlineStr">
         <is>
-          <t>0.9145299145299145, 0.9017094017094017, 0.8717948717948718, 0.9230769230769231, 0.9017094017094017, 0.9102564102564102, 0.9017094017094017</t>
+          <t>0.8846153846153846, 0.9017094017094017, 0.8675213675213675, 0.9230769230769231, 0.9017094017094017, 0.9102564102564102, 0.8760683760683761</t>
         </is>
       </c>
       <c r="CY3" t="n">
-        <v>0.9035409035409038</v>
+        <v>0.8949938949938951</v>
       </c>
       <c r="CZ3" t="n">
         <v>0.9017094017094017</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.01495414983384114</v>
+        <v>0.01825386616327968</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.9360344137655063</v>
+        <v>0.9410964385754302</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.9404761904761905</v>
+        <v>0.9411764705882353</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.010584782102798</v>
+        <v>0.0125034492833532</v>
       </c>
       <c r="DE3" t="inlineStr">
         <is>
-          <t>0.9747150997150997, 0.9751131221719457, 0.9748617395676219, 0.9776269482151835, 0.9793866264454499, 0.9855203619909502, 0.9733534439416792</t>
+          <t>0.9711538461538461, 0.9747611865258924, 0.9703871292106586, 0.9782302664655607, 0.979587732528909, 0.9854198089492207, 0.9723981900452489</t>
         </is>
       </c>
       <c r="DF3" t="n">
-        <v>0.9772253345782758</v>
+        <v>0.975991165697048</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.9751131221719457</v>
+        <v>0.9747611865258924</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.003872629129441545</v>
+        <v>0.005015339141132952</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TabNetModel_splashing_smote_first_launch</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{'estimator': 'PytorchTabularEstimator', 'estimator_params': {'model_class': 'TabNetModelConfig', 'model_config_params': {'n_d': 8, 'n_a': 8, 'n_steps': 3, 'gamma': 1.2, 'n_independent': 1, 'n_shared': 1, 'virtual_batch_size': 32, 'learning_rate': 0.001}, 'trainer_config_params': {'max_epochs': 300, 'early_stopping': 'valid_loss', 'early_stopping_patience': 15}, 'optimizer_config_params': {'optimizer': 'Adam', 'lr_scheduler': 'ReduceLROnPlateau', 'lr_scheduler_params': {'patience': 5, 'factor': 0.5}}}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.7999999999999999</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.8657407407407407</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.7638888888888888</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6363636363636364</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.8114478114478114</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.9146341463414634</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.8426966292134832</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.8948164682539683</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0.8037012557832123</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.8239583333333333</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.6842105263157895</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.7647058823529413</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>44.409635066986084, 71.98321509361267, 50.883962869644165, 59.03954887390137, 57.1475989818573, 94.14445519447327, 41.38849496841431</t>
+        </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>59.85670157841274</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>57.1475989818573</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>16.86461177658715</v>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.025656938552856445, 0.06457304954528809, 0.027042150497436523, 0.07705926895141602, 0.02678203582763672, 0.03596067428588867, 0.04569411277770996</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.04325260434831892</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.03596067428588867</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.01889917253918469</v>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.8333333333333334, 0.6792452830188679, 0.7735849056603774, 0.7924528301886793, 0.8490566037735849, 0.7547169811320755, 0.7169811320754716</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.8473684210526315, 0.7166666666666667, 0.7886996904024768, 0.8150154798761611, 0.8475232198142415, 0.7856037151702786, 0.686532507739938</t>
+        </is>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.7839156715317704</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.7886996904024768</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.05740957520018049</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.7713387241689128</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.7735849056603774</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.05612038494247176</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0.8615384615384616, 0.711864406779661, 0.806451612903226, 0.819672131147541, 0.8787878787878787, 0.7796610169491526, 0.782608695652174</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.7906976744186046, 0.6382978723404256, 0.7272727272727272, 0.7555555555555555, 0.8, 0.7234042553191489, 0.5945945945945946</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.7185460970715793</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.7272727272727272</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0.07082553690809877</v>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.8261180679785332, 0.6750811395600433, 0.7668621700879765, 0.7876138433515483, 0.8393939393939394, 0.7515326361341508, 0.6886016451233843</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>0.7621719202327965</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.7668621700879765</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.05834897939433521</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0.8057977433940134</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0.806451612903226</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0.05164694132400423</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.875, 0.8928571428571429, 0.9259259259259259, 0.90625, 0.92, 0.7714285714285715</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>0.7083333333333334, 0.5172413793103449, 0.64, 0.6538461538461539, 0.7619047619047619, 0.6071428571428571, 0.6111111111111112</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>0.6427970852355089</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.07235922716037323</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>0.8892564247921391</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>0.90625</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>0.05157655757853033</v>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>0.8, 0.6, 0.7352941176470589, 0.7352941176470589, 0.8529411764705882, 0.6764705882352942, 0.7941176470588235</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.8333333333333334, 0.8421052631578947, 0.8947368421052632, 0.8421052631578947, 0.8947368421052632, 0.5789473684210527</t>
+        </is>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.825814536340852</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.8421052631578947</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.1040477631811883</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.7420168067226891</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.7352941176470589</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.07831824574576308</v>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0.9308270676691729, 0.7603174603174603, 0.8839009287925697, 0.8653250773993808, 0.8529411764705882, 0.8529411764705883, 0.7368421052631579</t>
+        </is>
+      </c>
+      <c r="BR4" t="n">
+        <v>0.8404421417689881</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>0.8529411764705883</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>0.063406450059225</v>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>0.7327044025157232, 0.8213166144200627, 0.768025078369906, 0.8181818181818182, 0.7836990595611285, 0.8275862068965517, 0.768025078369906</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>0.7470105763004533, 0.8337184424475823, 0.7704484921384999, 0.8292593865452358, 0.8045579517140649, 0.8485265057135493, 0.7844316522037975</t>
+        </is>
+      </c>
+      <c r="BW4" t="n">
+        <v>0.8025647152947404</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>0.8045579517140649</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>0.03432229905072066</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0.7885054654735851</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0.7836990595611285</v>
+      </c>
+      <c r="CB4" t="n">
+        <v>0.03264596766234434</v>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>0.7708894878706198, 0.8503937007874016, 0.809278350515464, 0.8489583333333334, 0.8140161725067385, 0.8533333333333333, 0.8021390374331551</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>0.6792452830188679, 0.7782101167315174, 0.704, 0.7716535433070867, 0.7415730337078651, 0.7908745247148289, 0.7196969696969697</t>
+        </is>
+      </c>
+      <c r="CE4" t="n">
+        <v>0.7407504958824479</v>
+      </c>
+      <c r="CF4" t="n">
+        <v>0.7415730337078651</v>
+      </c>
+      <c r="CG4" t="n">
+        <v>0.03863391827876463</v>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>0.7250673854447438, 0.8143019087594595, 0.7566391752577319, 0.81030593832021, 0.7777946031073018, 0.822103929024081, 0.7609180035650625</t>
+        </is>
+      </c>
+      <c r="CI4" t="n">
+        <v>0.7810187062112272</v>
+      </c>
+      <c r="CJ4" t="n">
+        <v>0.7777946031073018</v>
+      </c>
+      <c r="CK4" t="n">
+        <v>0.03336562384673903</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>0.8212869165400065</v>
+      </c>
+      <c r="CM4" t="n">
+        <v>0.8140161725067385</v>
+      </c>
+      <c r="CN4" t="n">
+        <v>0.02864436243064156</v>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>0.8614457831325302, 0.9204545454545454, 0.8626373626373627, 0.9157303370786517, 0.9151515151515152, 0.9467455621301775, 0.8928571428571429</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>0.5921052631578947, 0.6993006993006993, 0.6423357664233577, 0.6950354609929078, 0.6428571428571429, 0.6933333333333334, 0.6291390728476821</t>
+        </is>
+      </c>
+      <c r="CQ4" t="n">
+        <v>0.6563009627018597</v>
+      </c>
+      <c r="CR4" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="CS4" t="n">
+        <v>0.03771198043729306</v>
+      </c>
+      <c r="CT4" t="n">
+        <v>0.9021460354917038</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>0.9151515151515152</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>0.02923238019586813</v>
+      </c>
+      <c r="CW4" t="inlineStr">
+        <is>
+          <t>0.697560975609756, 0.7902439024390244, 0.7621359223300971, 0.7912621359223301, 0.7330097087378641, 0.7766990291262136, 0.7281553398058253</t>
+        </is>
+      </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>0.7964601769911505, 0.8771929824561403, 0.7787610619469026, 0.8672566371681416, 0.8761061946902655, 0.9203539823008849, 0.8407079646017699</t>
+        </is>
+      </c>
+      <c r="CY4" t="n">
+        <v>0.8509770000221792</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>0.8672566371681416</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>0.04580958291715</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>0.7541524305673014</v>
+      </c>
+      <c r="DC4" t="n">
+        <v>0.7621359223300971</v>
+      </c>
+      <c r="DD4" t="n">
+        <v>0.03290085975719233</v>
+      </c>
+      <c r="DE4" t="inlineStr">
+        <is>
+          <t>0.8267860997194043, 0.916816431322208, 0.8537889853080162, 0.8881132399690695, 0.8671492396253974, 0.9097001460606581, 0.8803806168914855</t>
+        </is>
+      </c>
+      <c r="DF4" t="n">
+        <v>0.8775335369851769</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>0.8803806168914855</v>
+      </c>
+      <c r="DH4" t="n">
+        <v>0.02914204684736638</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TabNetModel_no_fragmentation_smotenc_first_launch</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{'estimator': 'PytorchTabularEstimator', 'estimator_params': {'model_class': 'TabNetModelConfig', 'model_config_params': {'n_d': 8, 'n_a': 8, 'n_steps': 3, 'gamma': 1.2, 'n_independent': 1, 'n_shared': 1, 'virtual_batch_size': 32, 'learning_rate': 0.001}, 'trainer_config_params': {'max_epochs': 300, 'early_stopping': 'valid_loss', 'early_stopping_patience': 15}, 'optimizer_config_params': {'optimizer': 'Adam', 'lr_scheduler': 'ReduceLROnPlateau', 'lr_scheduler_params': {'patience': 5, 'factor': 0.5}}}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7307692307692307</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.8260869565217392</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.9600000000000001</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.8745819397993311</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.9113636363636364</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.9795918367346939</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8727272727272727</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.8855218855218855</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.7184466019417476</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.9367088607594937</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.8131868131868132</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.9610962722099641</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0.8653312706710765</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.901840668911857</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.9742268041237113</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.8669724770642202</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0.9174757281553397</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>55.10281801223755, 74.42437982559204, 70.16506695747375, 57.28480005264282, 64.71836400032043, 55.42416787147522, 74.26288104057312</t>
+        </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>64.48321110861642</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>64.71836400032043</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8.006093420039628</v>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.03353285789489746, 0.02637791633605957, 0.06023812294006348, 0.02450704574584961, 0.02476811408996582, 0.02586817741394043, 0.025758981704711914</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.03157874516078404</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.02586817741394043</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.01204219350338673</v>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.7962962962962963, 0.7547169811320755, 0.8679245283018868, 0.8490566037735849, 0.8867924528301887, 0.8301886792452831, 0.8679245283018868</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.858974358974359, 0.7646520146520146, 0.8644688644688645, 0.8516483516483516, 0.9001831501831502, 0.7930402930402931, 0.9102564102564102</t>
+        </is>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.8490319204604919</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0.858974358974359</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.04922820668565793</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.8361285814116003</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0.043103974198503</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.7317073170731707, 0.6285714285714286, 0.7741935483870968, 0.75, 0.8125000000000001, 0.689655172413793, 0.8</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.835820895522388, 0.8169014084507042, 0.9066666666666667, 0.8918918918918919, 0.9189189189189189, 0.8831168831168831, 0.9014084507042254</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.8792464450388111</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.8918918918918919</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0.03538461689170347</v>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.7837641062977794, 0.7227364185110664, 0.8404301075268817, 0.8209459459459459, 0.8657094594594594, 0.7863860277653381, 0.8507042253521127</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>0.8100966129797975</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0.8209459459459459</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0.04577427869508031</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0.7409467809207841</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.05992718293054747</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.5769230769230769, 0.5238095238095238, 0.7058823529411765, 0.6666666666666666, 0.7222222222222222, 0.6666666666666666, 0.6666666666666666</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>1.0, 0.90625, 0.9444444444444444, 0.9428571428571428, 0.9714285714285714, 0.8947368421052632, 1.0</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>0.9513881429764889</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.03872182627998232</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0.6469767394137141</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0.06587055739625487</v>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>1.0, 0.7857142857142857, 0.8571428571428571, 0.8571428571428571, 0.9285714285714286, 0.7142857142857143, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>0.717948717948718, 0.7435897435897436, 0.8717948717948718, 0.8461538461538461, 0.8717948717948718, 0.8717948717948718, 0.8205128205128205</t>
+        </is>
+      </c>
+      <c r="BK5" t="n">
+        <v>0.8205128205128205</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.8461538461538461</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.05974178179597103</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.8775510204081634</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.09893224198808835</v>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0.9452991452991454, 0.7967032967032966, 0.9194139194139195, 0.8443223443223443, 0.945054945054945, 0.8113553113553114, 0.967032967032967</t>
+        </is>
+      </c>
+      <c r="BR5" t="n">
+        <v>0.8898831327402756</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0.9194139194139195</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0.0653167158998309</v>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>0.8647798742138365, 0.877742946708464, 0.8620689655172413, 0.8589341692789969, 0.8495297805642633, 0.8620689655172413, 0.8808777429467085</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>0.8966727716727717, 0.8941930618401206, 0.8947461035696329, 0.8813725490196078, 0.8787078934137758, 0.9022373051784817, 0.9038210155857214</t>
+        </is>
+      </c>
+      <c r="BW5" t="n">
+        <v>0.8931072428971589</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0.8947461035696329</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0.008942396059205516</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0.8651432063923931</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0.8620689655172413</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>0.01005480857789257</v>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>0.7902439024390244, 0.802030456852792, 0.7884615384615384, 0.7783251231527094, 0.7692307692307693, 0.7924528301886793, 0.8099999999999999</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>0.9002320185614849, 0.9115646258503401, 0.8976744186046511, 0.896551724137931, 0.8883720930232558, 0.8967136150234741, 0.91324200913242</t>
+        </is>
+      </c>
+      <c r="CE5" t="n">
+        <v>0.9006215006190796</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>0.8976744186046511</v>
+      </c>
+      <c r="CG5" t="n">
+        <v>0.008191884926287736</v>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>0.8452379605002547, 0.856797541351566, 0.8430679785330948, 0.8374384236453203, 0.8288014311270125, 0.8445832226060768, 0.86162100456621</t>
+        </is>
+      </c>
+      <c r="CI5" t="n">
+        <v>0.8453639374756479</v>
+      </c>
+      <c r="CJ5" t="n">
+        <v>0.8445832226060768</v>
+      </c>
+      <c r="CK5" t="n">
+        <v>0.01026816667023127</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>0.790106374332216</v>
+      </c>
+      <c r="CM5" t="n">
+        <v>0.7902439024390244</v>
+      </c>
+      <c r="CN5" t="n">
+        <v>0.01265339653995577</v>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>0.6694214876033058, 0.7053571428571429, 0.6666666666666666, 0.6694915254237288, 0.6504065040650406, 0.6614173228346457, 0.7043478260869566</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>0.9847715736040609, 0.9710144927536232, 0.9846938775510204, 0.9701492537313433, 0.9744897959183674, 0.9947916666666666, 0.9803921568627451</t>
+        </is>
+      </c>
+      <c r="CQ5" t="n">
+        <v>0.9800432595839752</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>0.9803921568627451</v>
+      </c>
+      <c r="CS5" t="n">
+        <v>0.00821038873892499</v>
+      </c>
+      <c r="CT5" t="n">
+        <v>0.6753012107910695</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>0.6694214876033058</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>0.01964852819401739</v>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>0.9642857142857143, 0.9294117647058824, 0.9647058823529412, 0.9294117647058824, 0.9411764705882353, 0.9882352941176471, 0.9529411764705882</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>0.8290598290598291, 0.8589743589743589, 0.8247863247863247, 0.8333333333333334, 0.8162393162393162, 0.8162393162393162, 0.8547008547008547</t>
+        </is>
+      </c>
+      <c r="CY5" t="n">
+        <v>0.8333333333333333</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>0.8290598290598291</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>0.01598998883236726</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>0.9528811524609845</v>
+      </c>
+      <c r="DC5" t="n">
+        <v>0.9529411764705882</v>
+      </c>
+      <c r="DD5" t="n">
+        <v>0.01985098451510961</v>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>0.9540598290598291, 0.9404725992961287, 0.9472599296128708, 0.9423831070889894, 0.9603821015585722, 0.965560583207642, 0.9640522875816994</t>
+        </is>
+      </c>
+      <c r="DF5" t="n">
+        <v>0.9534529196293903</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>0.9540598290598291</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>0.009537194934686195</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling4_6-neural_networks.xlsx
+++ b/results/metrics_modelling4_6-neural_networks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH5"/>
+  <dimension ref="A1:DH7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2548,6 +2548,786 @@
       </c>
       <c r="DH5" t="n">
         <v>0.009537194934686195</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>splashing</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CategoryEmbeddingModel_splashing_smote_opt-model</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{'estimator': 'PytorchTabularEstimator', 'estimator_params': {'model_class': 'CategoryEmbeddingModelConfig', 'trainer_config_params': {'max_epochs': 300, 'batch_size': 300, 'early_stopping': 'valid_loss', 'early_stopping_patience': 10, 'accelerator': 'gpu', 'devices': 1, 'progress_bar': 'none'}, 'optimizer_config_params': {'optimizer': 'Adam', 'lr_scheduler': 'ReduceLROnPlateau', 'lr_scheduler_params': {'patience': 5, 'factor': 0.5}}, 'model_config_params': {'activation': 'LeakyReLU', 'dropout': 0.05368731404192041, 'learning_rate': 0.010100246162580432, 'use_batch_norm': False, 'batch_norm_continuous_input': True, 'layers': '128'}}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8533333333333334</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8775510204081632</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8958333333333334</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.8865979381443299</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.9220679012345679</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.8395253841665045</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.8368055555555556</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.8076923076923077</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.7777777777777778</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.7924528301886792</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.8922558922558923</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.9444444444444444</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.8854166666666666</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9139784946236558</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.9593005952380952</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0.8849171752397558</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.8950892857142857</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.811965811965812</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0.8558558558558558</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>1.0455152988433838, 2.822162389755249, 0.9511258602142334, 1.748558521270752, 1.6606271266937256, 1.165550947189331, 1.687471866607666</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.583001715796334</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.660627126693726</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.5906765900268036</v>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.021254301071166992, 0.03110504150390625, 0.03519082069396973, 0.03544902801513672, 0.031102895736694336, 0.03302192687988281, 0.030825138092041016</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.03113559314182826</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.03110504150390625</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.004413407554968602</v>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.7735849056603774, 0.9056603773584906, 0.8490566037735849, 0.9622641509433962, 0.8490566037735849, 0.8301886792452831</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.9330827067669173, 0.7611111111111111, 0.903250773993808, 0.8475232198142415, 0.9473684210526316, 0.8591331269349844, 0.8212074303405572</t>
+        </is>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.8675252557163216</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0.8591331269349844</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.06081452303130598</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.873465109314166</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0.8490566037735849</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.06210627511558647</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0.9577464788732395, 0.823529411764706, 0.9253731343283583, 0.8787878787878787, 0.9714285714285714, 0.8749999999999999, 0.8656716417910447</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.918918918918919, 0.6842105263157895, 0.8717948717948718, 0.8, 0.9444444444444444, 0.8095238095238095, 0.7692307692307692</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.8283033343183719</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.8095238095238095</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0.0836638768397777</v>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.9383326988960792, 0.7538699690402477, 0.898584003061615, 0.8393939393939394, 0.9579365079365079, 0.8422619047619047, 0.8174512055109069</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>0.8639757469430286</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0.8422619047619047</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0.06646038969565106</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0.8996481595676855</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0.8787878787878787</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.04954185412513377</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.8484848484848485, 0.9393939393939394, 0.90625, 0.9444444444444444, 0.9333333333333333, 0.8787878787878788</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>0.9444444444444444, 0.65, 0.85, 0.7619047619047619, 1.0, 0.7391304347826086, 0.75</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>0.8136399487331164</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0.7619047619047619</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.1147781781500156</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0.9135912698412698</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0.03477145784916613</v>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.9714285714285714, 0.8, 0.9117647058823529, 0.8529411764705882, 1.0, 0.8235294117647058, 0.8529411764705882</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.8947368421052632, 0.7222222222222222, 0.8947368421052632, 0.8421052631578947, 0.8947368421052632, 0.8947368421052632, 0.7894736842105263</t>
+        </is>
+      </c>
+      <c r="BK6" t="n">
+        <v>0.8475355054302423</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.06326356014833588</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.8875150060024009</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.07012859637223683</v>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0.9834586466165414, 0.8777777777777778, 0.9860681114551083, 0.9226006191950464, 0.9628482972136223, 0.9071207430340558, 0.8978328173374615</t>
+        </is>
+      </c>
+      <c r="BR6" t="n">
+        <v>0.9339581446613734</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0.9226006191950464</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0.04019755084189896</v>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>0.8584905660377359, 0.9341692789968652, 0.8652037617554859, 0.9028213166144201, 0.8996865203761756, 0.8840125391849529, 0.9059561128526645</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>0.872372113101662, 0.9312580231065468, 0.8736575307156972, 0.9047813386029728, 0.8923661826617407, 0.8862230432167713, 0.9132013059541197</t>
+        </is>
+      </c>
+      <c r="BW6" t="n">
+        <v>0.8962656481942159</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0.8923661826617407</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0.01993520765672447</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0.8929057279740429</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0.8996865203761756</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>0.02404811350633178</v>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>0.8825065274151435, 0.9484029484029484, 0.8900255754475703, 0.9226932668329177, 0.921951219512195, 0.9072681704260651, 0.9242424242424243</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>0.8221343873517787, 0.9090909090909091, 0.8259109311740891, 0.8691983122362869, 0.8596491228070176, 0.8451882845188284, 0.8760330578512397</t>
+        </is>
+      </c>
+      <c r="CE6" t="n">
+        <v>0.8581721435757357</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>0.8596491228070176</v>
+      </c>
+      <c r="CG6" t="n">
+        <v>0.0281414211708796</v>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>0.8523204573834611, 0.9287469287469288, 0.8579682533108297, 0.8959457895346024, 0.8908001711596063, 0.8762282274724468, 0.9001377410468321</t>
+        </is>
+      </c>
+      <c r="CI6" t="n">
+        <v>0.8860210812363867</v>
+      </c>
+      <c r="CJ6" t="n">
+        <v>0.8908001711596063</v>
+      </c>
+      <c r="CK6" t="n">
+        <v>0.0243917751141534</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>0.9138700188970379</v>
+      </c>
+      <c r="CM6" t="n">
+        <v>0.9219512195121951</v>
+      </c>
+      <c r="CN6" t="n">
+        <v>0.0208363556074919</v>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>0.949438202247191, 0.9554455445544554, 0.9405405405405406, 0.9487179487179487, 0.9264705882352942, 0.9378238341968912, 0.9631578947368421</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>0.7428571428571429, 0.8974358974358975, 0.7611940298507462, 0.8306451612903226, 0.8521739130434782, 0.8015873015873016, 0.8217054263565892</t>
+        </is>
+      </c>
+      <c r="CQ6" t="n">
+        <v>0.8153712674887824</v>
+      </c>
+      <c r="CR6" t="n">
+        <v>0.8217054263565892</v>
+      </c>
+      <c r="CS6" t="n">
+        <v>0.04891088204035585</v>
+      </c>
+      <c r="CT6" t="n">
+        <v>0.9459420790327375</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>0.9487179487179487</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>0.01121765170544328</v>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>0.824390243902439, 0.9414634146341463, 0.8446601941747572, 0.8980582524271845, 0.9174757281553398, 0.8786407766990292, 0.8883495145631068</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>0.9203539823008849, 0.9210526315789473, 0.9026548672566371, 0.911504424778761, 0.8672566371681416, 0.8938053097345132, 0.9380530973451328</t>
+        </is>
+      </c>
+      <c r="CY6" t="n">
+        <v>0.9078115643090026</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>0.911504424778761</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>0.02113999073337604</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>0.884719732079429</v>
+      </c>
+      <c r="DC6" t="n">
+        <v>0.8883495145631068</v>
+      </c>
+      <c r="DD6" t="n">
+        <v>0.03735019536015502</v>
+      </c>
+      <c r="DE6" t="inlineStr">
+        <is>
+          <t>0.9502482192963523, 0.9822849807445443, 0.9425423146318412, 0.972656585617321, 0.9707663888650228, 0.9600481140991494, 0.9749763725405962</t>
+        </is>
+      </c>
+      <c r="DF6" t="n">
+        <v>0.9647889965421182</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>0.9707663888650228</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>0.01328987420691922</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>df_dimless</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>no_fragmentation</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CategoryEmbeddingModel_no_fragmentation_smotenc_opt-model</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{'estimator': 'PytorchTabularEstimator', 'estimator_params': {'model_class': 'CategoryEmbeddingModelConfig', 'trainer_config_params': {'max_epochs': 300, 'batch_size': 300, 'early_stopping': 'valid_loss', 'early_stopping_patience': 10, 'accelerator': 'gpu', 'devices': 1, 'progress_bar': 'none'}, 'optimizer_config_params': {'optimizer': 'Adam', 'lr_scheduler': 'ReduceLROnPlateau', 'lr_scheduler_params': {'patience': 5, 'factor': 0.5}}, 'model_config_params': {'activation': 'LeakyReLU', 'dropout': 0.020012990188122446, 'learning_rate': 0.051818480542551844, 'use_batch_norm': False, 'batch_norm_continuous_input': True, 'layers': '128'}}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8933333333333333</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.7894736842105262</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.9572727272727273</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.8590225563909774</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.8477272727272727</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9122807017543859</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.9454545454545454</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.9285714285714285</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.9393939393939394</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8674698795180723</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.9113924050632911</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.9806642666356985</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0.9236111111111112</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.9304668447334804</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.9672897196261683</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.9495412844036697</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.9583333333333334</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>1.2609286308288574, 1.5858442783355713, 1.6516401767730713, 0.9509181976318359, 1.1848039627075195, 1.284769058227539, 1.8354003429412842</t>
+        </is>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.39347209249224</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.284769058227539</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.2847903623229752</v>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.09030795097351074, 0.03214716911315918, 0.03312182426452637, 0.0426630973815918, 0.03192734718322754, 0.016433000564575195, 0.03195929527282715</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.03979424067905971</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0.03214716911315918</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0.02181705110790425</v>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.9074074074074074, 0.8867924528301887, 0.9622641509433962, 0.9245283018867925, 0.8867924528301887, 0.8867924528301887, 0.9433962264150944</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.9153846153846155, 0.9001831501831502, 0.9514652014652014, 0.9258241758241759, 0.8315018315018314, 0.8315018315018314, 0.9615384615384616</t>
+        </is>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.9024856096284667</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.9153846153846155</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0.04881452885379466</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0.9139962064490368</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.9074074074074074</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.02820492758291179</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>0.8484848484848485, 0.8125000000000001, 0.9285714285714286, 0.8666666666666666, 0.7692307692307692, 0.7692307692307692, 0.9032258064516129</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.9189189189189189, 0.9743589743589743, 0.9473684210526315, 0.9249999999999999, 0.9249999999999999, 0.9600000000000001</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.9405685210948368</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.9333333333333333</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.01916628981964416</v>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.8909090909090909, 0.8657094594594594, 0.9514652014652014, 0.9070175438596491, 0.8471153846153845, 0.8471153846153845, 0.9316129032258065</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>0.891563566878568</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.8909090909090909</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.03789294241633237</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0.8425586126622994</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0.8484848484848485</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.05775873079532773</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.7777777777777778, 0.7222222222222222, 0.9285714285714286, 0.8125, 0.8333333333333334, 0.8333333333333334, 0.8235294117647058</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>0.9722222222222222, 0.9714285714285714, 0.9743589743589743, 0.972972972972973, 0.9024390243902439, 0.9024390243902439, 1.0</t>
+        </is>
+      </c>
+      <c r="BC7" t="n">
+        <v>0.956551541394747</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0.9722222222222222</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.03545170133409956</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0.8187525010004001</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0.8235294117647058</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0.05799548443661851</v>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>0.9333333333333333, 0.9285714285714286, 0.9285714285714286, 0.9285714285714286, 0.7142857142857143, 0.7142857142857143, 1.0</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>0.8974358974358975, 0.8717948717948718, 0.9743589743589743, 0.9230769230769231, 0.9487179487179487, 0.9487179487179487, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.9267399267399269</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.03193332559370455</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.8782312925170068</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.106383770352787</v>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0.9692307692307692, 0.9322344322344323, 0.9835164835164836, 0.9487179487179487, 0.9725274725274725, 0.9413919413919414, 0.9926739926739927</t>
+        </is>
+      </c>
+      <c r="BR7" t="n">
+        <v>0.9628990057561486</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0.9692307692307692</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0.0208682982459598</v>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>0.9150943396226415, 0.9529780564263323, 0.9310344827586207, 0.9122257053291536, 0.9310344827586207, 0.9310344827586207, 0.9278996865203761</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>0.9270451770451771, 0.9604575163398692, 0.9380090497737557, 0.8952237305178481, 0.9267722473604827, 0.9492458521870286, 0.9321266968325792</t>
+        </is>
+      </c>
+      <c r="BW7" t="n">
+        <v>0.9326971814366772</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0.9321266968325792</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0.01906509756698112</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0.9287573194534807</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0.9310344827586207</v>
+      </c>
+      <c r="CB7" t="n">
+        <v>0.01232249589354134</v>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>0.8556149732620322, 0.9171270718232044, 0.8804347826086957, 0.8390804597701149, 0.8764044943820225, 0.8842105263157894, 0.8743169398907105</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>0.9398663697104677, 0.9671772428884027, 0.9515418502202644, 0.939655172413793, 0.9521739130434783, 0.9508928571428572, 0.9494505494505495</t>
+        </is>
+      </c>
+      <c r="CE7" t="n">
+        <v>0.9501082792671163</v>
+      </c>
+      <c r="CF7" t="n">
+        <v>0.9508928571428572</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>0.008559738087521994</v>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>0.8977406714862499, 0.9421521573558036, 0.91598831641448, 0.889367816091954, 0.9142892037127504, 0.9175516917293234, 0.91188374467063</t>
+        </is>
+      </c>
+      <c r="CI7" t="n">
+        <v>0.9127105144944557</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>0.9142892037127504</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>0.01546029427372632</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>0.8753127497217957</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>0.8764044943820225</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>0.02254141571874112</v>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>0.7766990291262136, 0.8645833333333334, 0.8181818181818182, 0.8202247191011236, 0.8387096774193549, 0.8, 0.8163265306122449</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>0.9813953488372092, 0.9910313901345291, 0.9818181818181818, 0.9478260869565217, 0.9690265486725663, 0.9953271028037384, 0.9773755656108597</t>
+        </is>
+      </c>
+      <c r="CQ7" t="n">
+        <v>0.977685746404801</v>
+      </c>
+      <c r="CR7" t="n">
+        <v>0.9813953488372092</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>0.01457414057581606</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>0.8192464439677269</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>0.02570596221319831</v>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>0.9523809523809523, 0.9764705882352941, 0.9529411764705882, 0.8588235294117647, 0.9176470588235294, 0.9882352941176471, 0.9411764705882353</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>0.9017094017094017, 0.9444444444444444, 0.9230769230769231, 0.9316239316239316, 0.9358974358974359, 0.9102564102564102, 0.9230769230769231</t>
+        </is>
+      </c>
+      <c r="CY7" t="n">
+        <v>0.9242979242979245</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>0.9230769230769231</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>0.01365120865384486</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>0.9410964385754301</v>
+      </c>
+      <c r="DC7" t="n">
+        <v>0.9523809523809523</v>
+      </c>
+      <c r="DD7" t="n">
+        <v>0.03974876751322907</v>
+      </c>
+      <c r="DE7" t="inlineStr">
+        <is>
+          <t>0.9783272283272283, 0.9855203619909502, 0.9809954751131222, 0.9697838109602814, 0.9786324786324787, 0.9828557063851181, 0.9814982403217698</t>
+        </is>
+      </c>
+      <c r="DF7" t="n">
+        <v>0.9796590431044213</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>0.9809954751131222</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>0.004630491909295781</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics_modelling4_6-neural_networks.xlsx
+++ b/results/metrics_modelling4_6-neural_networks.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DH7"/>
+  <dimension ref="A1:DH6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2568,766 +2568,376 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>{'estimator': 'PytorchTabularEstimator', 'estimator_params': {'model_class': 'CategoryEmbeddingModelConfig', 'trainer_config_params': {'max_epochs': 300, 'batch_size': 300, 'early_stopping': 'valid_loss', 'early_stopping_patience': 10, 'accelerator': 'gpu', 'devices': 1, 'progress_bar': 'none'}, 'optimizer_config_params': {'optimizer': 'Adam', 'lr_scheduler': 'ReduceLROnPlateau', 'lr_scheduler_params': {'patience': 5, 'factor': 0.5}}, 'model_config_params': {'activation': 'LeakyReLU', 'dropout': 0.05368731404192041, 'learning_rate': 0.010100246162580432, 'use_batch_norm': False, 'batch_norm_continuous_input': True, 'layers': '128'}}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
+          <t>{'estimator': 'PytorchTabularEstimator', 'estimator_params': {'model_class': 'CategoryEmbeddingModelConfig', 'trainer_config_params': {'max_epochs': 300, 'batch_size': 300, 'early_stopping': 'valid_loss', 'early_stopping_patience': 10, 'accelerator': 'gpu', 'devices': 1, 'progress_bar': 'none'}, 'optimizer_config_params': {'optimizer': 'Adam', 'lr_scheduler': 'ReduceLROnPlateau', 'lr_scheduler_params': {'patience': 5, 'factor': 0.5}}, 'model_config_params': {'activation': 'ReLU', 'dropout': 0.12063675406353806, 'learning_rate': 0.010999581868953563, 'use_batch_norm': False, 'batch_norm_continuous_input': True, 'layers': '128'}}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': ('inclination', 'volume_fraction'), 'passthrough_features': ('wettability',), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': False, 'smote_params': {}, 'random_state': 42}</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.8533333333333334</v>
+        <v>0.8133333333333334</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8775510204081632</v>
+        <v>0.8269230769230769</v>
       </c>
       <c r="G6" t="n">
         <v>0.8958333333333334</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8865979381443299</v>
+        <v>0.86</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9220679012345679</v>
+        <v>0.8958333333333334</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8395253841665045</v>
+        <v>0.79</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8368055555555556</v>
+        <v>0.78125</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8076923076923077</v>
+        <v>0.7826086956521739</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7924528301886792</v>
+        <v>0.72</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8922558922558923</v>
+        <v>0.9023569023569024</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9444444444444444</v>
+        <v>0.9267015706806283</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8854166666666666</v>
+        <v>0.921875</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9139784946236558</v>
+        <v>0.9242819843342037</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9593005952380952</v>
+        <v>0.952951388888889</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8849171752397558</v>
+        <v>0.8934206130201825</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8950892857142857</v>
+        <v>0.8942708333333333</v>
       </c>
       <c r="V6" t="n">
-        <v>0.811965811965812</v>
+        <v>0.8584905660377359</v>
       </c>
       <c r="W6" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="X6" t="n">
-        <v>0.8558558558558558</v>
+        <v>0.8625592417061612</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>1.0455152988433838, 2.822162389755249, 0.9511258602142334, 1.748558521270752, 1.6606271266937256, 1.165550947189331, 1.687471866607666</t>
+          <t>1.2052509784698486, 1.2054443359375, 1.2191855907440186, 1.5888311862945557, 2.6861276626586914, 1.4826538562774658, 1.9853689670562744</t>
         </is>
       </c>
       <c r="Z6" t="n">
-        <v>1.583001715796334</v>
+        <v>1.624694653919765</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.660627126693726</v>
+        <v>1.482653856277466</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5906765900268036</v>
+        <v>0.5062931385532728</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0.021254301071166992, 0.03110504150390625, 0.03519082069396973, 0.03544902801513672, 0.031102895736694336, 0.03302192687988281, 0.030825138092041016</t>
+          <t>0.0312504768371582, 0.03312563896179199, 0.031681060791015625, 0.030777692794799805, 0.0356142520904541, 0.03489208221435547, 0.033148765563964844</t>
         </is>
       </c>
       <c r="AD6" t="n">
-        <v>0.03113559314182826</v>
+        <v>0.03292713846479144</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.03110504150390625</v>
+        <v>0.03312563896179199</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.004413407554968602</v>
+        <v>0.001696808982661119</v>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.9444444444444444, 0.7735849056603774, 0.9056603773584906, 0.8490566037735849, 0.9622641509433962, 0.8490566037735849, 0.8301886792452831</t>
+          <t>0.9444444444444444, 0.8113207547169812, 0.9056603773584906, 0.8679245283018868, 0.9245283018867925, 0.8113207547169812, 0.8113207547169812</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.9330827067669173, 0.7611111111111111, 0.903250773993808, 0.8475232198142415, 0.9473684210526316, 0.8591331269349844, 0.8212074303405572</t>
+          <t>0.9330827067669173, 0.8031746031746032, 0.914860681114551, 0.8738390092879257, 0.9179566563467492, 0.8297213622291022, 0.794891640866873</t>
         </is>
       </c>
       <c r="AI6" t="n">
-        <v>0.8675252557163216</v>
+        <v>0.8667895228266745</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.8591331269349844</v>
+        <v>0.8738390092879257</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.06081452303130598</v>
+        <v>0.0534035917342563</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.873465109314166</v>
+        <v>0.868074273734651</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.8490566037735849</v>
+        <v>0.8679245283018868</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.06210627511558647</v>
+        <v>0.05357915858245822</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>0.9577464788732395, 0.823529411764706, 0.9253731343283583, 0.8787878787878787, 0.9714285714285714, 0.8749999999999999, 0.8656716417910447</t>
+          <t>0.9577464788732395, 0.8529411764705883, 0.923076923076923, 0.8923076923076922, 0.9411764705882353, 0.8387096774193549, 0.8529411764705882</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.918918918918919, 0.6842105263157895, 0.8717948717948718, 0.8, 0.9444444444444444, 0.8095238095238095, 0.7692307692307692</t>
+          <t>0.918918918918919, 0.7368421052631577, 0.8780487804878049, 0.8292682926829269, 0.8947368421052632, 0.7727272727272727, 0.7368421052631579</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.8283033343183719</v>
+        <v>0.8239120453497859</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.8095238095238095</v>
+        <v>0.8292682926829269</v>
       </c>
       <c r="AS6" t="n">
-        <v>0.0836638768397777</v>
+        <v>0.07049231287323876</v>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.9383326988960792, 0.7538699690402477, 0.898584003061615, 0.8393939393939394, 0.9579365079365079, 0.8422619047619047, 0.8174512055109069</t>
+          <t>0.9383326988960792, 0.794891640866873, 0.900562851782364, 0.8607879924953096, 0.9179566563467492, 0.8057184750733137, 0.794891640866873</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>0.8639757469430286</v>
+        <v>0.859020279475366</v>
       </c>
       <c r="AV6" t="n">
-        <v>0.8422619047619047</v>
+        <v>0.8607879924953096</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.06646038969565106</v>
+        <v>0.05676884639655286</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.8996481595676855</v>
+        <v>0.8941285136009459</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.8787878787878787</v>
+        <v>0.8923076923076922</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.04954185412513377</v>
+        <v>0.04402292008056208</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.9444444444444444, 0.8484848484848485, 0.9393939393939394, 0.90625, 0.9444444444444444, 0.9333333333333333, 0.8787878787878788</t>
+          <t>0.9444444444444444, 0.8787878787878788, 0.967741935483871, 0.9354838709677419, 0.9411764705882353, 0.9285714285714286, 0.8529411764705882</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.9444444444444444, 0.65, 0.85, 0.7619047619047619, 1.0, 0.7391304347826086, 0.75</t>
+          <t>0.9444444444444444, 0.7, 0.8181818181818182, 0.7727272727272727, 0.8947368421052632, 0.68, 0.7368421052631579</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>0.8136399487331164</v>
+        <v>0.7924189261031366</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.7619047619047619</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.1147781781500156</v>
+        <v>0.09172961653360312</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.9135912698412698</v>
+        <v>0.9213067436163126</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.9333333333333333</v>
+        <v>0.9354838709677419</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.03477145784916613</v>
+        <v>0.03745827682372321</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>0.9714285714285714, 0.8, 0.9117647058823529, 0.8529411764705882, 1.0, 0.8235294117647058, 0.8529411764705882</t>
+          <t>0.9714285714285714, 0.8285714285714286, 0.8823529411764706, 0.8529411764705882, 0.9411764705882353, 0.7647058823529411, 0.8529411764705882</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>0.8947368421052632, 0.7222222222222222, 0.8947368421052632, 0.8421052631578947, 0.8947368421052632, 0.8947368421052632, 0.7894736842105263</t>
+          <t>0.8947368421052632, 0.7777777777777778, 0.9473684210526315, 0.8947368421052632, 0.8947368421052632, 0.8947368421052632, 0.7368421052631579</t>
         </is>
       </c>
       <c r="BK6" t="n">
-        <v>0.8475355054302423</v>
+        <v>0.8629908103592313</v>
       </c>
       <c r="BL6" t="n">
         <v>0.8947368421052632</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.06326356014833588</v>
+        <v>0.07002609720867461</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.8875150060024009</v>
+        <v>0.8705882352941176</v>
       </c>
       <c r="BO6" t="n">
         <v>0.8529411764705882</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.07012859637223683</v>
+        <v>0.06424195640580728</v>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>0.9834586466165414, 0.8777777777777778, 0.9860681114551083, 0.9226006191950464, 0.9628482972136223, 0.9071207430340558, 0.8978328173374615</t>
+          <t>0.9849624060150375, 0.8634920634920634, 0.9860681114551083, 0.931888544891641, 0.958204334365325, 0.9040247678018576, 0.890092879256966</t>
         </is>
       </c>
       <c r="BR6" t="n">
-        <v>0.9339581446613734</v>
+        <v>0.9312475867539998</v>
       </c>
       <c r="BS6" t="n">
-        <v>0.9226006191950464</v>
+        <v>0.931888544891641</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.04019755084189896</v>
+        <v>0.04414788711856033</v>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.8584905660377359, 0.9341692789968652, 0.8652037617554859, 0.9028213166144201, 0.8996865203761756, 0.8840125391849529, 0.9059561128526645</t>
+          <t>0.8584905660377359, 0.890282131661442, 0.8589341692789969, 0.9059561128526645, 0.9153605015673981, 0.8746081504702194, 0.9122257053291536</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>0.872372113101662, 0.9312580231065468, 0.8736575307156972, 0.9047813386029728, 0.8923661826617407, 0.8862230432167713, 0.9132013059541197</t>
+          <t>0.872372113101662, 0.889323919554985, 0.8688031617836584, 0.9092061173640347, 0.9104948878769654, 0.8769438955236704, 0.9140604862960735</t>
         </is>
       </c>
       <c r="BW6" t="n">
-        <v>0.8962656481942159</v>
+        <v>0.8916006545001498</v>
       </c>
       <c r="BX6" t="n">
-        <v>0.8923661826617407</v>
+        <v>0.889323919554985</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.01993520765672447</v>
+        <v>0.01805093984900737</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.8929057279740429</v>
+        <v>0.8879796195996587</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.8996865203761756</v>
+        <v>0.890282131661442</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.02404811350633178</v>
+        <v>0.02254544582770811</v>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.8825065274151435, 0.9484029484029484, 0.8900255754475703, 0.9226932668329177, 0.921951219512195, 0.9072681704260651, 0.9242424242424243</t>
+          <t>0.8825065274151435, 0.9127182044887782, 0.884318766066838, 0.9250000000000002, 0.9339853300733497, 0.8994974874371858, 0.9303482587064676</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0.8221343873517787, 0.9090909090909091, 0.8259109311740891, 0.8691983122362869, 0.8596491228070176, 0.8451882845188284, 0.8760330578512397</t>
+          <t>0.8221343873517787, 0.8523206751054853, 0.8192771084337348, 0.8739495798319328, 0.8820960698689956, 0.8333333333333335, 0.8813559322033898</t>
         </is>
       </c>
       <c r="CE6" t="n">
-        <v>0.8581721435757357</v>
+        <v>0.8520667265898073</v>
       </c>
       <c r="CF6" t="n">
-        <v>0.8596491228070176</v>
+        <v>0.8523206751054853</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0281414211708796</v>
+        <v>0.02552474091963724</v>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>0.8523204573834611, 0.9287469287469288, 0.8579682533108297, 0.8959457895346024, 0.8908001711596063, 0.8762282274724468, 0.9001377410468321</t>
+          <t>0.8523204573834611, 0.8825194397971317, 0.8517979372502864, 0.8994747899159665, 0.9080406999711726, 0.8664154103852597, 0.9058520954549287</t>
         </is>
       </c>
       <c r="CI6" t="n">
-        <v>0.8860210812363867</v>
+        <v>0.8809172614511723</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.8908001711596063</v>
+        <v>0.8825194397971317</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0243917751141534</v>
+        <v>0.02261602349554817</v>
       </c>
       <c r="CL6" t="n">
-        <v>0.9138700188970379</v>
+        <v>0.9097677963125375</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.9219512195121951</v>
+        <v>0.9127182044887782</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0208363556074919</v>
+        <v>0.01981009294751581</v>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>0.949438202247191, 0.9554455445544554, 0.9405405405405406, 0.9487179487179487, 0.9264705882352942, 0.9378238341968912, 0.9631578947368421</t>
+          <t>0.949438202247191, 0.9336734693877551, 0.9398907103825137, 0.9536082474226805, 0.9408866995073891, 0.9322916666666666, 0.9540816326530612</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
         <is>
-          <t>0.7428571428571429, 0.8974358974358975, 0.7611940298507462, 0.8306451612903226, 0.8521739130434782, 0.8015873015873016, 0.8217054263565892</t>
+          <t>0.7428571428571429, 0.8211382113821138, 0.75, 0.832, 0.8706896551724138, 0.7874015748031497, 0.8455284552845529</t>
         </is>
       </c>
       <c r="CQ6" t="n">
-        <v>0.8153712674887824</v>
+        <v>0.8070878627856247</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.8217054263565892</v>
+        <v>0.8211382113821138</v>
       </c>
       <c r="CS6" t="n">
-        <v>0.04891088204035585</v>
+        <v>0.04490156442906437</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.9459420790327375</v>
+        <v>0.9434100897524653</v>
       </c>
       <c r="CU6" t="n">
-        <v>0.9487179487179487</v>
+        <v>0.9408866995073891</v>
       </c>
       <c r="CV6" t="n">
-        <v>0.01121765170544328</v>
+        <v>0.008378518668209902</v>
       </c>
       <c r="CW6" t="inlineStr">
         <is>
-          <t>0.824390243902439, 0.9414634146341463, 0.8446601941747572, 0.8980582524271845, 0.9174757281553398, 0.8786407766990292, 0.8883495145631068</t>
+          <t>0.824390243902439, 0.8926829268292683, 0.8349514563106796, 0.8980582524271845, 0.9271844660194175, 0.8689320388349514, 0.9077669902912622</t>
         </is>
       </c>
       <c r="CX6" t="inlineStr">
         <is>
-          <t>0.9203539823008849, 0.9210526315789473, 0.9026548672566371, 0.911504424778761, 0.8672566371681416, 0.8938053097345132, 0.9380530973451328</t>
+          <t>0.9203539823008849, 0.8859649122807017, 0.9026548672566371, 0.9203539823008849, 0.8938053097345132, 0.8849557522123894, 0.9203539823008849</t>
         </is>
       </c>
       <c r="CY6" t="n">
-        <v>0.9078115643090026</v>
+        <v>0.9040632554838423</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.911504424778761</v>
+        <v>0.9026548672566371</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.02113999073337604</v>
+        <v>0.01509975901910118</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.884719732079429</v>
+        <v>0.8791380535164574</v>
       </c>
       <c r="DC6" t="n">
-        <v>0.8883495145631068</v>
+        <v>0.8926829268292683</v>
       </c>
       <c r="DD6" t="n">
-        <v>0.03735019536015502</v>
+        <v>0.03530166337841305</v>
       </c>
       <c r="DE6" t="inlineStr">
         <is>
-          <t>0.9502482192963523, 0.9822849807445443, 0.9425423146318412, 0.972656585617321, 0.9707663888650228, 0.9600481140991494, 0.9749763725405962</t>
+          <t>0.9486941506583207, 0.9559264013692769, 0.9454205687773864, 0.963119683821634, 0.9765228971561131, 0.9630122862788899, 0.9745467823696194</t>
         </is>
       </c>
       <c r="DF6" t="n">
-        <v>0.9647889965421182</v>
+        <v>0.9610346814901772</v>
       </c>
       <c r="DG6" t="n">
-        <v>0.9707663888650228</v>
+        <v>0.9630122862788899</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.01328987420691922</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>df_dimless</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>no_fragmentation</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>CategoryEmbeddingModel_no_fragmentation_smotenc_opt-model</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>{'estimator': 'PytorchTabularEstimator', 'estimator_params': {'model_class': 'CategoryEmbeddingModelConfig', 'trainer_config_params': {'max_epochs': 300, 'batch_size': 300, 'early_stopping': 'valid_loss', 'early_stopping_patience': 10, 'accelerator': 'gpu', 'devices': 1, 'progress_bar': 'none'}, 'optimizer_config_params': {'optimizer': 'Adam', 'lr_scheduler': 'ReduceLROnPlateau', 'lr_scheduler_params': {'patience': 5, 'factor': 0.5}}, 'model_config_params': {'activation': 'LeakyReLU', 'dropout': 0.020012990188122446, 'learning_rate': 0.051818480542551844, 'use_batch_norm': False, 'batch_norm_continuous_input': True, 'layers': '128'}}, 'source_features': ('init_volume_fraction', 'volume_fraction', 'sedimentation_Re', 'sign_sedimentation_Re', 'sign_sedimentation_Stk', 'sedimentation_Stk', 'particle_liquid_density_ratio', 'particle_droplet_diameter_ratio', 'sign_particle_droplet_diameter_ratio', 'wettability', 'relative_roughness', 'inclination', 'Re', 'We', 'K'), 'features_to_drop': ('Re', 'We', 'init_volume_fraction', 'particle_liquid_density_ratio', 'sedimentation_Re', 'sign_particle_droplet_diameter_ratio', 'sign_sedimentation_Re', 'sign_sedimentation_Stk'), 'log_features': ('relative_roughness', 'sedimentation_Stk', 'particle_droplet_diameter_ratio'), 'minmax_features': (), 'passthrough_features': ('wettability', 'inclination', 'volume_fraction'), 'std_features': ('sedimentation_Stk', 'particle_droplet_diameter_ratio', 'relative_roughness', 'K'), 'add_init_transformer': True, 'add_df_transformer': True, 'add_const': False, 'add_smote': True, 'is_smotenc': True, 'smote_params': {'categorical_features': ('wettability', 'inclination')}, 'random_state': 42}</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.8933333333333333</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.8333333333333334</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.7894736842105262</v>
-      </c>
-      <c r="I7" t="n">
-        <v>0.9572727272727273</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.8590225563909774</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.8477272727272727</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.9122807017543859</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.9454545454545454</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.9285714285714285</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.9393939393939394</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0.8674698795180723</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.9113924050632911</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.8888888888888888</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.9806642666356985</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0.9236111111111112</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0.9304668447334804</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0.9672897196261683</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0.9495412844036697</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.9583333333333334</v>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>1.2609286308288574, 1.5858442783355713, 1.6516401767730713, 0.9509181976318359, 1.1848039627075195, 1.284769058227539, 1.8354003429412842</t>
-        </is>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.39347209249224</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.284769058227539</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>0.2847903623229752</v>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0.09030795097351074, 0.03214716911315918, 0.03312182426452637, 0.0426630973815918, 0.03192734718322754, 0.016433000564575195, 0.03195929527282715</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.03979424067905971</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0.03214716911315918</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>0.02181705110790425</v>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>0.9074074074074074, 0.8867924528301887, 0.9622641509433962, 0.9245283018867925, 0.8867924528301887, 0.8867924528301887, 0.9433962264150944</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.9153846153846155, 0.9001831501831502, 0.9514652014652014, 0.9258241758241759, 0.8315018315018314, 0.8315018315018314, 0.9615384615384616</t>
-        </is>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.9024856096284667</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0.9153846153846155</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>0.04881452885379466</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0.9139962064490368</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.9074074074074074</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>0.02820492758291179</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>0.8484848484848485, 0.8125000000000001, 0.9285714285714286, 0.8666666666666666, 0.7692307692307692, 0.7692307692307692, 0.9032258064516129</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>0.9333333333333333, 0.9189189189189189, 0.9743589743589743, 0.9473684210526315, 0.9249999999999999, 0.9249999999999999, 0.9600000000000001</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.9405685210948368</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.9333333333333333</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0.01916628981964416</v>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>0.8909090909090909, 0.8657094594594594, 0.9514652014652014, 0.9070175438596491, 0.8471153846153845, 0.8471153846153845, 0.9316129032258065</t>
-        </is>
-      </c>
-      <c r="AU7" t="n">
-        <v>0.891563566878568</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.8909090909090909</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.03789294241633237</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0.8425586126622994</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0.8484848484848485</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.05775873079532773</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>0.7777777777777778, 0.7222222222222222, 0.9285714285714286, 0.8125, 0.8333333333333334, 0.8333333333333334, 0.8235294117647058</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>0.9722222222222222, 0.9714285714285714, 0.9743589743589743, 0.972972972972973, 0.9024390243902439, 0.9024390243902439, 1.0</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>0.956551541394747</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0.9722222222222222</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0.03545170133409956</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.8187525010004001</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0.8235294117647058</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0.05799548443661851</v>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>0.9333333333333333, 0.9285714285714286, 0.9285714285714286, 0.9285714285714286, 0.7142857142857143, 0.7142857142857143, 1.0</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>0.8974358974358975, 0.8717948717948718, 0.9743589743589743, 0.9230769230769231, 0.9487179487179487, 0.9487179487179487, 0.9230769230769231</t>
-        </is>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.9267399267399269</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.03193332559370455</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>0.8782312925170068</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>0.106383770352787</v>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>0.9692307692307692, 0.9322344322344323, 0.9835164835164836, 0.9487179487179487, 0.9725274725274725, 0.9413919413919414, 0.9926739926739927</t>
-        </is>
-      </c>
-      <c r="BR7" t="n">
-        <v>0.9628990057561486</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>0.9692307692307692</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>0.0208682982459598</v>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>0.9150943396226415, 0.9529780564263323, 0.9310344827586207, 0.9122257053291536, 0.9310344827586207, 0.9310344827586207, 0.9278996865203761</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>0.9270451770451771, 0.9604575163398692, 0.9380090497737557, 0.8952237305178481, 0.9267722473604827, 0.9492458521870286, 0.9321266968325792</t>
-        </is>
-      </c>
-      <c r="BW7" t="n">
-        <v>0.9326971814366772</v>
-      </c>
-      <c r="BX7" t="n">
-        <v>0.9321266968325792</v>
-      </c>
-      <c r="BY7" t="n">
-        <v>0.01906509756698112</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>0.9287573194534807</v>
-      </c>
-      <c r="CA7" t="n">
-        <v>0.9310344827586207</v>
-      </c>
-      <c r="CB7" t="n">
-        <v>0.01232249589354134</v>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>0.8556149732620322, 0.9171270718232044, 0.8804347826086957, 0.8390804597701149, 0.8764044943820225, 0.8842105263157894, 0.8743169398907105</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>0.9398663697104677, 0.9671772428884027, 0.9515418502202644, 0.939655172413793, 0.9521739130434783, 0.9508928571428572, 0.9494505494505495</t>
-        </is>
-      </c>
-      <c r="CE7" t="n">
-        <v>0.9501082792671163</v>
-      </c>
-      <c r="CF7" t="n">
-        <v>0.9508928571428572</v>
-      </c>
-      <c r="CG7" t="n">
-        <v>0.008559738087521994</v>
-      </c>
-      <c r="CH7" t="inlineStr">
-        <is>
-          <t>0.8977406714862499, 0.9421521573558036, 0.91598831641448, 0.889367816091954, 0.9142892037127504, 0.9175516917293234, 0.91188374467063</t>
-        </is>
-      </c>
-      <c r="CI7" t="n">
-        <v>0.9127105144944557</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>0.9142892037127504</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>0.01546029427372632</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>0.8753127497217957</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>0.8764044943820225</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>0.02254141571874112</v>
-      </c>
-      <c r="CO7" t="inlineStr">
-        <is>
-          <t>0.7766990291262136, 0.8645833333333334, 0.8181818181818182, 0.8202247191011236, 0.8387096774193549, 0.8, 0.8163265306122449</t>
-        </is>
-      </c>
-      <c r="CP7" t="inlineStr">
-        <is>
-          <t>0.9813953488372092, 0.9910313901345291, 0.9818181818181818, 0.9478260869565217, 0.9690265486725663, 0.9953271028037384, 0.9773755656108597</t>
-        </is>
-      </c>
-      <c r="CQ7" t="n">
-        <v>0.977685746404801</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>0.9813953488372092</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>0.01457414057581606</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>0.8192464439677269</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="CV7" t="n">
-        <v>0.02570596221319831</v>
-      </c>
-      <c r="CW7" t="inlineStr">
-        <is>
-          <t>0.9523809523809523, 0.9764705882352941, 0.9529411764705882, 0.8588235294117647, 0.9176470588235294, 0.9882352941176471, 0.9411764705882353</t>
-        </is>
-      </c>
-      <c r="CX7" t="inlineStr">
-        <is>
-          <t>0.9017094017094017, 0.9444444444444444, 0.9230769230769231, 0.9316239316239316, 0.9358974358974359, 0.9102564102564102, 0.9230769230769231</t>
-        </is>
-      </c>
-      <c r="CY7" t="n">
-        <v>0.9242979242979245</v>
-      </c>
-      <c r="CZ7" t="n">
-        <v>0.9230769230769231</v>
-      </c>
-      <c r="DA7" t="n">
-        <v>0.01365120865384486</v>
-      </c>
-      <c r="DB7" t="n">
-        <v>0.9410964385754301</v>
-      </c>
-      <c r="DC7" t="n">
-        <v>0.9523809523809523</v>
-      </c>
-      <c r="DD7" t="n">
-        <v>0.03974876751322907</v>
-      </c>
-      <c r="DE7" t="inlineStr">
-        <is>
-          <t>0.9783272283272283, 0.9855203619909502, 0.9809954751131222, 0.9697838109602814, 0.9786324786324787, 0.9828557063851181, 0.9814982403217698</t>
-        </is>
-      </c>
-      <c r="DF7" t="n">
-        <v>0.9796590431044213</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>0.9809954751131222</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>0.004630491909295781</v>
+        <v>0.01103826845198495</v>
       </c>
     </row>
   </sheetData>
